--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1612,44 +1612,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131393400</v>
+        <v>134693690</v>
       </c>
       <c r="B10" t="n">
-        <v>57947</v>
+        <v>57796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1689,22 +1689,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131529957</v>
+        <v>131393400</v>
       </c>
       <c r="B11" t="n">
         <v>57947</v>
@@ -1768,7 +1768,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R11" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,22 +1808,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,27 +1850,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132437412</v>
+        <v>131529957</v>
       </c>
       <c r="B12" t="n">
-        <v>58563</v>
+        <v>57947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102987</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,40 +1969,44 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133180867</v>
+        <v>132437412</v>
       </c>
       <c r="B13" t="n">
-        <v>58308</v>
+        <v>58563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103008</v>
+        <v>102987</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2042,22 +2046,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133164798</v>
+        <v>133180867</v>
       </c>
       <c r="B14" t="n">
-        <v>58461</v>
+        <v>58308</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,37 +2099,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103018</v>
+        <v>103008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2135,10 +2131,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587329</v>
+        <v>587343</v>
       </c>
       <c r="R14" t="n">
-        <v>6550354</v>
+        <v>6550351</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2170,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,7 +2176,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,7 +2203,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133893874</v>
+        <v>133164798</v>
       </c>
       <c r="B15" t="n">
         <v>58461</v>
@@ -2237,14 +2233,18 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R15" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2284,22 +2284,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,44 +2326,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131393408</v>
+        <v>133893874</v>
       </c>
       <c r="B16" t="n">
-        <v>58112</v>
+        <v>58461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587329</v>
+        <v>587343</v>
       </c>
       <c r="R16" t="n">
-        <v>6550354</v>
+        <v>6550351</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2403,29 +2403,29 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130766037</v>
+        <v>131393408</v>
       </c>
       <c r="B17" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,21 +2456,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2485,11 +2485,7 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Transätter Gullsätra, Transätter Gullsätra, Flen, Srm</t>
@@ -2526,34 +2522,29 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Vid fågelmatning</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2573,37 +2564,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132437408</v>
+        <v>130766037</v>
       </c>
       <c r="B18" t="n">
-        <v>58375</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103037</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2613,17 +2604,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Transätter Gullsätra, Transätter Gullsätra, Flen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R18" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2650,22 +2645,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Vid fågelmatning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,27 +2692,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132437413</v>
+        <v>132437408</v>
       </c>
       <c r="B19" t="n">
-        <v>58596</v>
+        <v>58375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,45 +2811,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132437415</v>
+        <v>132437413</v>
       </c>
       <c r="B20" t="n">
-        <v>58624</v>
+        <v>58596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2897,7 +2893,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2907,7 +2903,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2934,27 +2930,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131718548</v>
+        <v>132437415</v>
       </c>
       <c r="B21" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2968,7 +2964,11 @@
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3011,22 +3011,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,42 +3053,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131501882</v>
+        <v>131718548</v>
       </c>
       <c r="B22" t="n">
-        <v>58676</v>
+        <v>58658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3126,22 +3130,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3168,27 +3172,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131393404</v>
+        <v>131501882</v>
       </c>
       <c r="B23" t="n">
-        <v>58085</v>
+        <v>58676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3198,16 +3202,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587329</v>
+        <v>587343</v>
       </c>
       <c r="R23" t="n">
-        <v>6550354</v>
+        <v>6550351</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3245,22 +3245,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3287,10 +3287,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133893870</v>
+        <v>131393404</v>
       </c>
       <c r="B24" t="n">
-        <v>58107</v>
+        <v>58085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3315,10 +3315,18 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3326,10 +3334,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R24" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3356,22 +3364,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,6 +3403,117 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133893870</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Transätter Gullsätra, Transätter Gullsätra, Flen, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>587343</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6550351</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Leif Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Leif Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93758347</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93758677</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131529956</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134079694</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134079695</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133294470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133893867</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134693690</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1847,6 +1897,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131393400</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1966,6 +2021,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131529957</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2085,6 +2145,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132437412</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2200,6 +2265,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133180867</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2323,6 +2393,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133164798</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2442,6 +2517,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133893874</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2561,6 +2641,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131393408</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2689,6 +2774,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130766037</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2808,6 +2898,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132437408</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2927,6 +3022,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132437413</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3050,6 +3150,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132437415</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3169,6 +3274,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134916688</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3288,6 +3398,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131718548</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3403,6 +3518,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131501882</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3522,6 +3642,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131393404</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3633,8 +3758,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133893870</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -3161,7 +3161,7 @@
         <v>134916688</v>
       </c>
       <c r="B22" t="n">
-        <v>58624</v>
+        <v>58629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
